--- a/out/Attention-Mamba1_repeat_4_000002.xlsx
+++ b/out/Attention-Mamba1_repeat_4_000002.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.069469496003421</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>2.247209366080289</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.4694694960034209</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.4694694960034209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.847209366080289</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.847209366080289</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.4694694960034209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.4694694960034209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.847209366080289</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.4694694960034209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.4694694960034209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.847209366080289</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.4694694960034209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.4694694960034209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.847209366080289</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.847209366080289</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.847209366080289</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.847209366080289</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.847209366080289</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.847209366080289</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37511,10 +37511,10 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.847209366080289</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38306,10 +38306,10 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.847209366080289</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39101,10 +39101,10 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.847209366080289</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39896,10 +39896,10 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>2.247209366080289</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40691,10 +40691,10 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.247209366080289</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41486,10 +41486,10 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.247209366080289</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42281,10 +42281,10 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>2.247209366080289</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43076,10 +43076,10 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.247209366080289</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43871,10 +43871,10 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.247209366080289</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44669,7 +44669,7 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45461,10 +45461,10 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.247209366080289</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46259,7 +46259,7 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47054,7 +47054,7 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47846,10 +47846,10 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.247209366080289</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48644,7 +48644,7 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50231,10 +50231,10 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.247209366080289</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.4694694960034209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.247209366080289</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53411,10 +53411,10 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.847209366080289</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.847209366080289</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55001,10 +55001,10 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>2.847209366080289</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.4694694960034209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58979,7 +58979,7 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59774,7 +59774,7 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60569,7 +60569,7 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62159,7 +62159,7 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62954,7 +62954,7 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63749,7 +63749,7 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64544,7 +64544,7 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65339,7 +65339,7 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66134,7 +66134,7 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67724,7 +67724,7 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69314,7 +69314,7 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70109,7 +70109,7 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74084,7 +74084,7 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74879,7 +74879,7 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.847209366080289</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.4694694960034209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>2.847209366080289</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.4694694960034209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.4694694960034209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-Mamba1_repeat_4_000002.xlsx
+++ b/out/Attention-Mamba1_repeat_4_000002.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.069469496003421</v>
+        <v>0.5695108125977835</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>2.247209366080289</v>
+        <v>0.1904617997882166</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.4694694960034209</v>
+        <v>0.3904617997882167</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.4694694960034209</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.069469496003421</v>
+        <v>0.1904617997882166</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.847209366080289</v>
+        <v>1.148559825407351</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.847209366080289</v>
+        <v>1.148559825407351</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.4694694960034209</v>
+        <v>0.3904617997882167</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.4694694960034209</v>
+        <v>-0.3676362258309172</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.069469496003421</v>
+        <v>0.3904617997882167</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.847209366080289</v>
+        <v>0.3904617997882167</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.4694694960034209</v>
+        <v>0.3904617997882167</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.4694694960034209</v>
+        <v>-0.3676362258309172</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.3676362258309172</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.069469496003421</v>
+        <v>0.3904617997882167</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.847209366080289</v>
+        <v>0.3904617997882167</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.4694694960034209</v>
+        <v>0.3904617997882167</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.4694694960034209</v>
+        <v>0.3904617997882167</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.847209366080289</v>
+        <v>1.148559825407351</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.847209366080289</v>
+        <v>1.906657851026484</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.847209366080289</v>
+        <v>1.906657851026484</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.847209366080289</v>
+        <v>1.906657851026484</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.847209366080289</v>
+        <v>1.906657851026484</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.847209366080289</v>
+        <v>1.906657851026484</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.847209366080289</v>
+        <v>1.906657851026484</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.847209366080289</v>
+        <v>1.906657851026484</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.847209366080289</v>
+        <v>1.906657851026484</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>2.247209366080289</v>
+        <v>1.906657851026484</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.247209366080289</v>
+        <v>1.706657851026484</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41489,7 +41489,7 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.247209366080289</v>
+        <v>1.706657851026484</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>2.247209366080289</v>
+        <v>1.706657851026484</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43079,7 +43079,7 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.247209366080289</v>
+        <v>1.706657851026484</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.247209366080289</v>
+        <v>0.9485598254073502</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44669,7 +44669,7 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.069469496003421</v>
+        <v>0.9485598254073505</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45464,7 +45464,7 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.247209366080289</v>
+        <v>0.1904617997882166</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46259,7 +46259,7 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.069469496003421</v>
+        <v>0.1904617997882166</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47054,7 +47054,7 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.069469496003421</v>
+        <v>0.1904617997882166</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47849,7 +47849,7 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.247209366080289</v>
+        <v>0.1904617997882166</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48644,7 +48644,7 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.069469496003421</v>
+        <v>0.1904617997882166</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.069469496003421</v>
+        <v>0.1904617997882166</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.247209366080289</v>
+        <v>0.1904617997882166</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.069469496003421</v>
+        <v>0.1904617997882166</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.4694694960034209</v>
+        <v>0.1904617997882166</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.247209366080289</v>
+        <v>1.148559825407351</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.847209366080289</v>
+        <v>1.906657851026484</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.847209366080289</v>
+        <v>1.906657851026484</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>2.847209366080289</v>
+        <v>1.148559825407351</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.4694694960034209</v>
+        <v>0.3904617997882167</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58979,7 +58979,7 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59774,7 +59774,7 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60569,7 +60569,7 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62159,7 +62159,7 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62954,7 +62954,7 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63749,7 +63749,7 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64544,7 +64544,7 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65339,7 +65339,7 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66134,7 +66134,7 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67724,7 +67724,7 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69314,7 +69314,7 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70109,7 +70109,7 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74084,7 +74084,7 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74879,7 +74879,7 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.069469496003421</v>
+        <v>0.3904617997882167</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.847209366080289</v>
+        <v>0.3904617997882167</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.4694694960034209</v>
+        <v>1.148559825407351</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>2.847209366080289</v>
+        <v>0.3904617997882167</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.4694694960034209</v>
+        <v>0.3904617997882167</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.4694694960034209</v>
+        <v>-0.3676362258309172</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.069469496003421</v>
+        <v>-0.5676362258309172</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-Mamba1_repeat_4_000002.xlsx
+++ b/out/Attention-Mamba1_repeat_4_000002.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.0002768021076917648</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.5695108125977835</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>1.65943056344986e-05</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.1904617997882166</v>
+        <v>-0.09000000000000005</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.0004092548042535782</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.3904617997882167</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.000615948811173439</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.5676362258309172</v>
+        <v>0.3</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.0004313122481107712</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.0007128696888685226</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.0007667448371648788</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.1904617997882166</v>
+        <v>-0.3</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>5.620531737804413e-05</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.148559825407351</v>
+        <v>-0.3</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.000487571582198143</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.148559825407351</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.0006629228591918945</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.3904617997882167</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.0006542708724737167</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3676362258309172</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.0006860531866550446</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.5676362258309172</v>
+        <v>0.16</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.0006067678332328796</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.001107880845665932</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.001166088506579399</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.001088831573724747</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.001088874414563179</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.00120946578681469</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.001325888559222221</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.001191200688481331</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.001254545524716377</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.001480096951127052</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.001235941424965858</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.3904617997882167</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.0006896685808897018</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.3904617997882167</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.0008065644651651382</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.3904617997882167</v>
+        <v>0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.0006760377436876297</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3676362258309172</v>
+        <v>0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.0003819447010755539</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3676362258309172</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.0007557328790426254</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.5676362258309172</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.001168830320239067</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.0012510996311903</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.00124245323240757</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.00149199552834034</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.001431901007890701</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.001283181831240654</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.0007753316313028336</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.3904617997882167</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>9.874813258647919e-05</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.3904617997882167</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.000499064102768898</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.3904617997882167</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.0005272217094898224</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.3904617997882167</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.000735914334654808</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.148559825407351</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.001031173393130302</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.906657851026484</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.002026010304689407</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.906657851026484</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.002771908417344093</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.906657851026484</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.002167975530028343</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.906657851026484</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,10 +36716,10 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.005669007077813148</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.906657851026484</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37511,10 +37511,10 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.0002835486084222794</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.906657851026484</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38306,10 +38306,10 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.001189369708299637</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.906657851026484</v>
+        <v>-0.16</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39101,10 +39101,10 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.0004691649228334427</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.906657851026484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39896,10 +39896,10 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.001300286501646042</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.906657851026484</v>
+        <v>-0.16</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40691,10 +40691,10 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.0002731271088123322</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.706657851026484</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41486,10 +41486,10 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.003301935270428658</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.706657851026484</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42281,10 +42281,10 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.001407697796821594</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.706657851026484</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43076,10 +43076,10 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.001107411459088326</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.706657851026484</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43871,10 +43871,10 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>6.201863288879395e-05</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.9485598254073502</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44666,10 +44666,10 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.0003649760037660599</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.9485598254073505</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45461,10 +45461,10 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.0001614000648260117</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.1904617997882166</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46256,10 +46256,10 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.0007764212787151337</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.1904617997882166</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47051,10 +47051,10 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.0005851853638887405</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.1904617997882166</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47846,10 +47846,10 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.0002979803830385208</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.1904617997882166</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48641,10 +48641,10 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.0001539736986160278</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.1904617997882166</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49436,10 +49436,10 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.0002578385174274445</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.1904617997882166</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50231,10 +50231,10 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.0006682183593511581</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.1904617997882166</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51026,10 +51026,10 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.0002039391547441483</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.1904617997882166</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51821,10 +51821,10 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.0006436463445425034</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.1904617997882166</v>
+        <v>0.16</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.0002263281494379044</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.148559825407351</v>
+        <v>0.16</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53411,10 +53411,10 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.0009765271097421646</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.906657851026484</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.001708673313260078</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.906657851026484</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55001,10 +55001,10 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.000557970255613327</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.148559825407351</v>
+        <v>0.16</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55796,10 +55796,10 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.0002684351056814194</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.3904617997882167</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56591,10 +56591,10 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.0004500765353441238</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57386,10 +57386,10 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.0006017051637172699</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58181,10 +58181,10 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.0005618389695882797</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58976,10 +58976,10 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.00108802504837513</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59771,10 +59771,10 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.0008228439837694168</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60566,10 +60566,10 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.001114543527364731</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61361,10 +61361,10 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.001602007076144218</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62156,10 +62156,10 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.001532150432467461</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62951,10 +62951,10 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.001365805044770241</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63746,10 +63746,10 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.001573154702782631</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64541,10 +64541,10 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.001666532829403877</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.001571191474795341</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.001546217128634453</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.001261262223124504</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.00156792439520359</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.001456471160054207</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69311,10 +69311,10 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.001544877886772156</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70106,10 +70106,10 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.001803597435355186</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.001352371647953987</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.001206981018185616</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.0003453046083450317</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.001406079158186913</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.5676362258309172</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.001344030722975731</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.5676362258309172</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74876,10 +74876,10 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.0009582303464412689</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.001572323963046074</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.001737652346491814</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.001807266846299171</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.001150822266936302</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.001720452681183815</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.001660363748669624</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.00175461545586586</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81236,10 +81236,10 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.001433933153748512</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82031,10 +82031,10 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.001993259415030479</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.001738747581839561</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.001570103690028191</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.001858225092291832</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.001696987077593803</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.001747220754623413</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.001936672255396843</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87596,10 +87596,10 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.001973351463675499</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.001899020746350288</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.002073613926768303</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.001693941652774811</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.001977870240807533</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.001782828941941261</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.001885561272501945</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.001745542511343956</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.5676362258309172</v>
+        <v>0.16</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.0003047548234462738</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.5676362258309172</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.0009426120668649673</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.3904617997882167</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.0009202193468809128</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.3904617997882167</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,10 +96341,10 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.0007824022322893143</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.148559825407351</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.0002108532935380936</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.3904617997882167</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97931,10 +97931,10 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.0007841363549232483</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.3904617997882167</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98726,10 +98726,10 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.000916721299290657</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3676362258309172</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99521,10 +99521,10 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.0005837399512529373</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.5676362258309172</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100316,10 +100316,10 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.001301556825637817</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.2300000000000001</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.0002672392874956131</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.5676362258309172</v>
+        <v>-0.3</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-Mamba1_repeat_4_000002.xlsx
+++ b/out/Attention-Mamba1_repeat_4_000002.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.0002768021076917648</v>
+        <v>-0.0002768076956272125</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.02000000000000007</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1.65943056344986e-05</v>
+        <v>1.658126711845398e-05</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.09000000000000005</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.0004092548042535782</v>
+        <v>-0.000409293919801712</v>
       </c>
       <c r="JB4" t="n">
         <v>0.4399999999999999</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.000615948811173439</v>
+        <v>-0.0006159525364637375</v>
       </c>
       <c r="JB5" t="n">
         <v>0.3</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.0007128696888685226</v>
+        <v>-0.0007128734141588211</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.4399999999999999</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.0007667448371648788</v>
+        <v>-0.0007667485624551773</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.3</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>5.620531737804413e-05</v>
+        <v>5.619041621685028e-05</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.3</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.000487571582198143</v>
+        <v>0.0004875864833593369</v>
       </c>
       <c r="JB10" t="n">
         <v>0.4399999999999999</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.0006629228591918945</v>
+        <v>-0.0006629209965467453</v>
       </c>
       <c r="JB11" t="n">
         <v>0.5799999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.0006542708724737167</v>
+        <v>-0.0006542634218931198</v>
       </c>
       <c r="JB12" t="n">
         <v>0.4399999999999999</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.0006860531866550446</v>
+        <v>-0.0006860624998807907</v>
       </c>
       <c r="JB13" t="n">
         <v>0.16</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.0006067678332328796</v>
+        <v>-0.0006067901849746704</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.5799999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.001107880845665932</v>
+        <v>-0.001107869669795036</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.7199999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.001166088506579399</v>
+        <v>-0.001166081055998802</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.8599999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-0.001088831573724747</v>
+        <v>-0.001088820397853851</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.9999999999999998</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.001088874414563179</v>
+        <v>-0.001088893041014671</v>
       </c>
       <c r="JB18" t="n">
         <v>-0.9999999999999998</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.00120946578681469</v>
+        <v>-0.001209458336234093</v>
       </c>
       <c r="JB19" t="n">
         <v>-0.9999999999999998</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-0.001325888559222221</v>
+        <v>-0.001325877383351326</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.9999999999999998</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>-0.001191200688481331</v>
+        <v>-0.00119117833673954</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.9999999999999998</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.001254545524716377</v>
+        <v>-0.001254534348845482</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.9999999999999998</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.001235941424965858</v>
+        <v>-0.001235919073224068</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.1199999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.0006896685808897018</v>
+        <v>0.0006896592676639557</v>
       </c>
       <c r="JB25" t="n">
         <v>0.02000000000000007</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.0008065644651651382</v>
+        <v>-0.0008065570145845413</v>
       </c>
       <c r="JB26" t="n">
         <v>0.3</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.0006760377436876297</v>
+        <v>-0.000676056370139122</v>
       </c>
       <c r="JB27" t="n">
         <v>0.3</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>-0.0003819447010755539</v>
+        <v>-0.0003819596022367477</v>
       </c>
       <c r="JB28" t="n">
         <v>0.02000000000000007</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>-0.0007557328790426254</v>
+        <v>-0.0007557570934295654</v>
       </c>
       <c r="JB29" t="n">
         <v>0.02000000000000007</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.001168830320239067</v>
+        <v>-0.001168837770819664</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.1199999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-0.0012510996311903</v>
+        <v>-0.001251107081770897</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.9999999999999998</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.00124245323240757</v>
+        <v>-0.001242451369762421</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.9999999999999998</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.00149199552834034</v>
+        <v>-0.001492025330662727</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.9999999999999998</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.001431901007890701</v>
+        <v>-0.001431897282600403</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.7199999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.001283181831240654</v>
+        <v>-0.001283174380660057</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.4399999999999999</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-0.0007753316313028336</v>
+        <v>-0.000775335356593132</v>
       </c>
       <c r="JB36" t="n">
         <v>0.4399999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>9.874813258647919e-05</v>
+        <v>9.875744581222534e-05</v>
       </c>
       <c r="JB37" t="n">
         <v>0.7199999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>-0.000499064102768898</v>
+        <v>-0.0004990790039300919</v>
       </c>
       <c r="JB38" t="n">
         <v>0.9999999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.0005272217094898224</v>
+        <v>-0.0005272235721349716</v>
       </c>
       <c r="JB39" t="n">
         <v>0.9999999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.000735914334654808</v>
+        <v>0.0007359012961387634</v>
       </c>
       <c r="JB40" t="n">
         <v>0.9999999999999998</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.001031173393130302</v>
+        <v>0.001031169667840004</v>
       </c>
       <c r="JB41" t="n">
         <v>0.9999999999999998</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.002026010304689407</v>
+        <v>0.002026047557592392</v>
       </c>
       <c r="JB42" t="n">
         <v>0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.002771908417344093</v>
+        <v>0.002771882340312004</v>
       </c>
       <c r="JB43" t="n">
         <v>0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.002167975530028343</v>
+        <v>0.002167945727705956</v>
       </c>
       <c r="JB44" t="n">
         <v>0.8599999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.005669007077813148</v>
+        <v>0.005668995901942253</v>
       </c>
       <c r="JB45" t="n">
         <v>0.1199999999999999</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.0002835486084222794</v>
+        <v>0.0002835337072610855</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.02000000000000007</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.001189369708299637</v>
+        <v>0.001189367845654488</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.16</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.001300286501646042</v>
+        <v>0.001300275325775146</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.16</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.0002731271088123322</v>
+        <v>0.0002731345593929291</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.02000000000000007</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.003301935270428658</v>
+        <v>0.003301938995718956</v>
       </c>
       <c r="JB51" t="n">
         <v>0.1199999999999999</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.001407697796821594</v>
+        <v>0.001407714560627937</v>
       </c>
       <c r="JB52" t="n">
         <v>0.5799999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>6.201863288879395e-05</v>
+        <v>6.201490759849548e-05</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.4399999999999999</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.0003649760037660599</v>
+        <v>-0.0003649983555078506</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.7199999999999999</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.0001614000648260117</v>
+        <v>0.0001613926142454147</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.9999999999999998</v>
@@ -46256,10 +46256,10 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.0007764212787151337</v>
+        <v>-0.0007764138281345367</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47051,10 +47051,10 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.0005851853638887405</v>
+        <v>-0.0005851965397596359</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47846,10 +47846,10 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.0002979803830385208</v>
+        <v>0.0002979859709739685</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48641,10 +48641,10 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.0001539736986160278</v>
+        <v>-0.0001539681106805801</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49436,10 +49436,10 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.0002578385174274445</v>
+        <v>-0.0002578515559434891</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.0006682183593511581</v>
+        <v>0.0006682369858026505</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.1199999999999999</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.0006436463445425034</v>
+        <v>-0.000643627718091011</v>
       </c>
       <c r="JB64" t="n">
         <v>0.16</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.0002263281494379044</v>
+        <v>0.0002262908965349197</v>
       </c>
       <c r="JB65" t="n">
         <v>0.16</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.0009765271097421646</v>
+        <v>0.0009765010327100754</v>
       </c>
       <c r="JB66" t="n">
         <v>0.1600000000000001</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.001708673313260078</v>
+        <v>0.001708664000034332</v>
       </c>
       <c r="JB67" t="n">
         <v>0.1600000000000001</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.000557970255613327</v>
+        <v>0.0005579721182584763</v>
       </c>
       <c r="JB68" t="n">
         <v>0.16</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.0002684351056814194</v>
+        <v>-0.0002684313803911209</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.1199999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.0004500765353441238</v>
+        <v>-0.0004500262439250946</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.0006017051637172699</v>
+        <v>-0.0006017163395881653</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.0005618389695882797</v>
+        <v>-0.000561865046620369</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.00108802504837513</v>
+        <v>-0.001088013872504234</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.0008228439837694168</v>
+        <v>-0.0008228514343500137</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.001114543527364731</v>
+        <v>-0.001114539802074432</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.001602007076144218</v>
+        <v>-0.001602014526724815</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.001532150432467461</v>
+        <v>-0.001532146707177162</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.001365805044770241</v>
+        <v>-0.001365790143609047</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.001573154702782631</v>
+        <v>-0.001573143526911736</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.9999999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.001666532829403877</v>
+        <v>-0.001666519790887833</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.9999999999999998</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.001571191474795341</v>
+        <v>-0.00157119520008564</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.9999999999999998</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.001546217128634453</v>
+        <v>-0.001546218991279602</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.9999999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.001261262223124504</v>
+        <v>-0.001261265948414803</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.9999999999999998</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.00156792439520359</v>
+        <v>-0.001567931845784187</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.9999999999999998</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.001456471160054207</v>
+        <v>-0.001456467434763908</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.9999999999999998</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.001544877886772156</v>
+        <v>-0.00154486857354641</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.9999999999999998</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.001803597435355186</v>
+        <v>-0.001803616061806679</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.9999999999999998</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.001352371647953987</v>
+        <v>-0.001352377235889435</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.1199999999999999</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.001206981018185616</v>
+        <v>-0.001207005232572556</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.1199999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.0003453046083450317</v>
+        <v>-0.0003452878445386887</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.1199999999999999</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.001406079158186913</v>
+        <v>-0.001406064257025719</v>
       </c>
       <c r="JB91" t="n">
         <v>0.02000000000000007</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.001344030722975731</v>
+        <v>-0.00134403258562088</v>
       </c>
       <c r="JB92" t="n">
         <v>0.02000000000000007</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.0009582303464412689</v>
+        <v>-0.0009582173079252243</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.2599999999999998</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.001572323963046074</v>
+        <v>-0.001572331413626671</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.2599999999999998</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.001737652346491814</v>
+        <v>-0.001737670972943306</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.7199999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.001807266846299171</v>
+        <v>-0.001807278022170067</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.8599999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.001150822266936302</v>
+        <v>-0.001150820404291153</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.8599999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.001720452681183815</v>
+        <v>-0.001720454543828964</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.8599999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.001660363748669624</v>
+        <v>-0.001660371199250221</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.7199999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>-0.00175461545586586</v>
+        <v>-0.001754619181156158</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.8599999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.001433933153748512</v>
+        <v>-0.001433897763490677</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.8599999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.001993259415030479</v>
+        <v>-0.001993255689740181</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.8599999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.001738747581839561</v>
+        <v>-0.001738755032420158</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.8599999999999999</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.001570103690028191</v>
+        <v>-0.001570113003253937</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.9999999999999998</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.001858225092291832</v>
+        <v>-0.001858221367001534</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.9999999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.001696987077593803</v>
+        <v>-0.00169697217643261</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.9999999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.001747220754623413</v>
+        <v>-0.001747209578752518</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.9999999999999998</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.001936672255396843</v>
+        <v>-0.001936651766300201</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.9999999999999998</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.001973351463675499</v>
+        <v>-0.001973332837224007</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.9999999999999998</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.001899020746350288</v>
+        <v>-0.001899009570479393</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.9999999999999998</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.002073613926768303</v>
+        <v>-0.002073630690574646</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.9999999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.001693941652774811</v>
+        <v>-0.00169394351541996</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.9999999999999998</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.001977870240807533</v>
+        <v>-0.001977851614356041</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.9999999999999998</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>-0.001782828941941261</v>
+        <v>-0.00178283266723156</v>
       </c>
       <c r="JB114" t="n">
         <v>-0.9999999999999998</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.001885561272501945</v>
+        <v>-0.001885576173663139</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.1199999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-0.001745542511343956</v>
+        <v>-0.00174550898373127</v>
       </c>
       <c r="JB116" t="n">
         <v>0.16</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.0003047548234462738</v>
+        <v>-0.00030476413667202</v>
       </c>
       <c r="JB117" t="n">
         <v>0.4399999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.0009426120668649673</v>
+        <v>-0.0009426139295101166</v>
       </c>
       <c r="JB118" t="n">
         <v>0.7199999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.0009202193468809128</v>
+        <v>0.0009202286601066589</v>
       </c>
       <c r="JB119" t="n">
         <v>0.9999999999999998</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.0007824022322893143</v>
+        <v>-0.0007823929190635681</v>
       </c>
       <c r="JB120" t="n">
         <v>0.8599999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.0002108532935380936</v>
+        <v>0.000210864469408989</v>
       </c>
       <c r="JB121" t="n">
         <v>0.8599999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>-0.0007841363549232483</v>
+        <v>-0.0007841270416975021</v>
       </c>
       <c r="JB122" t="n">
         <v>0.7199999999999999</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.000916721299290657</v>
+        <v>-0.0009167101234197617</v>
       </c>
       <c r="JB123" t="n">
         <v>0.5799999999999998</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>-0.0005837399512529373</v>
+        <v>-0.0005837325006723404</v>
       </c>
       <c r="JB124" t="n">
         <v>0.4399999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.001301556825637817</v>
+        <v>-0.001301540061831474</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.2300000000000001</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.0002672392874956131</v>
+        <v>-0.0002672262489795685</v>
       </c>
       <c r="JB126" t="n">
         <v>-0.3</v>
